--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-12  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-13  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-13  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-14  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-14  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-15  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-15  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-16  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-16  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-17  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-17  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-18  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-18  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-19  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-19  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-20  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-20  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-21  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-21  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-22  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-22  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-23  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-23  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-24  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-24  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-25  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-25  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-26  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-26  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-27  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-27  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-28  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-28  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-29  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-29  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-30  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-09-30  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-01  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-01  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-02  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-02  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-03  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-03  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-04  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-04  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-05  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-05  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-06  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-06  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-07  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-07  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-08  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-08  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-09  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-09  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-10  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-10  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-11  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-11  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-12  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-12  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-13  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-13  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-14  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-14  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-15  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-15  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-16  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-16  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-17  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-17  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-18  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-18  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-19  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-19  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-20  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-20  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-21  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-21  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-22  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-22  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-23  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-23  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-24  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-24  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-25  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-25  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-26  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-26  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-27  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-27  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-28  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-28  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-29  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-29  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-30  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>

--- a/LGC_Account_Flow_Tracker.xlsx
+++ b/LGC_Account_Flow_Tracker.xlsx
@@ -454,7 +454,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-30  |  Action type: Transfer accept (LGC only)</t>
+          <t>Source: CER REC Registry Public API  |  Last updated: 2026-10-31  |  Action type: Transfer accept (LGC only)</t>
         </is>
       </c>
     </row>
